--- a/fhir/ValueSet-DeleFoelelser.xlsx
+++ b/fhir/ValueSet-DeleFoelelser.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.23.0</t>
+    <t>2.23.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-DeleFoelelser.xlsx
+++ b/fhir/ValueSet-DeleFoelelser.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.23.1</t>
+    <t>2.23.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-DeleFoelelser.xlsx
+++ b/fhir/ValueSet-DeleFoelelser.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.23.2</t>
+    <t>2.23.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -99,13 +99,25 @@
     <t>heleTiden</t>
   </si>
   <si>
+    <t>Hele tiden</t>
+  </si>
+  <si>
     <t>forDetMeste</t>
   </si>
   <si>
+    <t>For det meste</t>
+  </si>
+  <si>
     <t>nogleGange</t>
   </si>
   <si>
+    <t>Nogle gange</t>
+  </si>
+  <si>
     <t>sjaeldent</t>
+  </si>
+  <si>
+    <t>Sjældent</t>
   </si>
   <si>
     <t>aldrig</t>
@@ -398,32 +410,40 @@
       <c r="A2" t="s" s="2">
         <v>27</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>28</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>29</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>32</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>34</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -436,10 +456,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/ValueSet-DeleFoelelser.xlsx
+++ b/fhir/ValueSet-DeleFoelelser.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.23.5</t>
+    <t>2.24.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-DeleFoelelser.xlsx
+++ b/fhir/ValueSet-DeleFoelelser.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.24.0</t>
+    <t>2.19.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -123,7 +123,7 @@
     <t>aldrig</t>
   </si>
   <si>
-    <t>Slet ikke</t>
+    <t>Aldrig</t>
   </si>
   <si>
     <t>System URI</t>

--- a/fhir/ValueSet-DeleFoelelser.xlsx
+++ b/fhir/ValueSet-DeleFoelelser.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.19.5</t>
+    <t>2.25.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -123,7 +123,7 @@
     <t>aldrig</t>
   </si>
   <si>
-    <t>Aldrig</t>
+    <t>Slet ikke</t>
   </si>
   <si>
     <t>System URI</t>

--- a/fhir/ValueSet-DeleFoelelser.xlsx
+++ b/fhir/ValueSet-DeleFoelelser.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.25.0</t>
+    <t>1.25.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-DeleFoelelser.xlsx
+++ b/fhir/ValueSet-DeleFoelelser.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.25.1</t>
+    <t>2.26.0</t>
   </si>
   <si>
     <t>Name</t>
